--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Ascension_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Ascension_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R81c2584f6e464ff7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Re7bb9523d8794a6e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Ra6360c37a76b42fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R33491428169344a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Rccbda0c77c26487e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R1288aa0ed9b04430"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R7b9593120aba4e8a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Rbfeb8f6bafa34d03"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Rcb4e44de97b34bd0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="Re876d81bf433472c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Rbe9a3840d89946e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Red270c8e9fc74523"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R91b5d5abd4984b3e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="Rf30b18ef590a41a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R97cfbd8797a14db8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="Ra6b1cfd686c64c25"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R7e701664cf4547d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R9ee8fd6aad1c4f9a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="Re58a10b977b840e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R7f79f703150e4e2e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R92de3e8caaeb4c78"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R0a833588add74914"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R555ff3855dd3432b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Rc35c96a834524ab2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="Rb217f83d5cc14226"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R1154e5ec685d4a72"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R9acaf519eb1942e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R42ffbb6459f54e71"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R591cc6c6757d4d33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Rc6e29e017c93495e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Rd5aa78169adb411a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R71a9591cf8964285"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Rc122590ae5174f90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R801db173fd894f3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R31cc87e4be38485a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R119558121f4541cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Rfb879c04cbbc4ea7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R99f886d4784f4ee3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R55e3ad83afb74948"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Rcd7d57af832c4494"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R6df3a89a8a874536"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R2768e26d88c44ee5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="Rd128d87afafb4ff2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R9be976f04f314295"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R4dda7d0678f94359"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Re4b1d8c1397b4bea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R7f238102c76d48ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R812475d7669f45c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Rcf8195d0663a4a09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="Rfdc4107584844be0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Rf170844071224af6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R09cc52cc2f0d49c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R2eabe604dc414640"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R491e2f6f0153485d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Rd53bfb7b3eec4d4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R35a63a3fe3fd471c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -174,7 +174,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="45">
+  <x:cellXfs count="43">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -230,12 +230,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
@@ -2156,7 +2150,7 @@
       <x:c r="A5" s="2" t="str">
         <x:v>Fiches suivies</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:f>SUM(B10:B35)</x:f>
         <x:v>158</x:v>
       </x:c>
@@ -2164,7 +2158,7 @@
       <x:c r="D5" s="2" t="str">
         <x:v>Intégrés</x:v>
       </x:c>
-      <x:c r="E5" s="33" t="n">
+      <x:c r="E5" s="31" t="n">
         <x:f>SUM(E10:F35)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2172,7 +2166,7 @@
       <x:c r="G5" s="2" t="str">
         <x:v>À vérifier</x:v>
       </x:c>
-      <x:c r="H5" s="33" t="n">
+      <x:c r="H5" s="31" t="n">
         <x:f>SUM(H10:H35)</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -2180,7 +2174,7 @@
       <x:c r="J5" s="2" t="str">
         <x:v>Extrapolations</x:v>
       </x:c>
-      <x:c r="K5" s="33" t="n">
+      <x:c r="K5" s="31" t="n">
         <x:f>SUM(I10:I35)</x:f>
         <x:v>130</x:v>
       </x:c>
@@ -2203,7 +2197,7 @@
       <x:c r="M6" s="2"/>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
-      <x:c r="A7" s="34" t="str">
+      <x:c r="A7" s="32" t="str">
         <x:v>Défini = spécification. Établi = référence documentée. Les colonnes d’adaptation restent des propositions.</x:v>
       </x:c>
       <x:c r="B7" s="2"/>
@@ -2235,95 +2229,95 @@
       <x:c r="M8" s="2"/>
     </x:row>
     <x:row r="9" ht="34" customHeight="1">
-      <x:c r="A9" s="30" t="str">
+      <x:c r="A9" s="28" t="str">
         <x:v>Domaine</x:v>
       </x:c>
-      <x:c r="B9" s="31" t="str">
+      <x:c r="B9" s="29" t="str">
         <x:v>Total</x:v>
       </x:c>
-      <x:c r="C9" s="31" t="str">
+      <x:c r="C9" s="29" t="str">
         <x:v>Défini</x:v>
       </x:c>
-      <x:c r="D9" s="31" t="str">
+      <x:c r="D9" s="29" t="str">
         <x:v>Prototype</x:v>
       </x:c>
-      <x:c r="E9" s="31" t="str">
+      <x:c r="E9" s="29" t="str">
         <x:v>Intégré</x:v>
       </x:c>
-      <x:c r="F9" s="31" t="str">
+      <x:c r="F9" s="29" t="str">
         <x:v>Validé</x:v>
       </x:c>
-      <x:c r="G9" s="31" t="str">
+      <x:c r="G9" s="29" t="str">
         <x:v>Établi</x:v>
       </x:c>
-      <x:c r="H9" s="31" t="str">
+      <x:c r="H9" s="29" t="str">
         <x:v>À vérifier</x:v>
       </x:c>
-      <x:c r="I9" s="31" t="str">
+      <x:c r="I9" s="29" t="str">
         <x:v>Extrapolation</x:v>
       </x:c>
-      <x:c r="J9" s="31" t="str">
+      <x:c r="J9" s="29" t="str">
         <x:v>Coupé attesté</x:v>
       </x:c>
-      <x:c r="K9" s="31" t="str">
+      <x:c r="K9" s="29" t="str">
         <x:v>Concept abandonné</x:v>
       </x:c>
-      <x:c r="L9" s="31" t="str">
+      <x:c r="L9" s="29" t="str">
         <x:v>Allégation écartée</x:v>
       </x:c>
-      <x:c r="M9" s="32" t="str">
+      <x:c r="M9" s="30" t="str">
         <x:v>Priorité P0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="22" customHeight="1">
-      <x:c r="A10" s="35" t="str">
+      <x:c r="A10" s="33" t="str">
         <x:v>Personnages</x:v>
       </x:c>
-      <x:c r="B10" s="39" t="n">
+      <x:c r="B10" s="37" t="n">
         <x:f>COUNTA('Personnages'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C10" s="39" t="n">
+      <x:c r="C10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D10" s="39" t="n">
+      <x:c r="D10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E10" s="39" t="n">
+      <x:c r="E10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F10" s="39" t="n">
+      <x:c r="F10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G10" s="39" t="n">
+      <x:c r="G10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$10,"Établi")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="H10" s="39" t="n">
+      <x:c r="H10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I10" s="39" t="n">
+      <x:c r="I10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J10" s="39" t="n">
+      <x:c r="J10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K10" s="39" t="n">
+      <x:c r="K10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L10" s="39" t="n">
+      <x:c r="L10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M10" s="39" t="n">
+      <x:c r="M10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2332,104 +2326,104 @@
       <x:c r="A11" s="2" t="str">
         <x:v>PNJ</x:v>
       </x:c>
-      <x:c r="B11" s="40" t="n">
+      <x:c r="B11" s="38" t="n">
         <x:f>COUNTA('PNJ'!$A$7:$A$12)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C11" s="40" t="n">
+      <x:c r="C11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$12,"Défini")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D11" s="40" t="n">
+      <x:c r="D11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$12,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E11" s="40" t="n">
+      <x:c r="E11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$12,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F11" s="40" t="n">
+      <x:c r="F11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$12,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G11" s="40" t="n">
+      <x:c r="G11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$12,"Établi")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H11" s="40" t="n">
+      <x:c r="H11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$12,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I11" s="40" t="n">
+      <x:c r="I11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$12,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J11" s="40" t="n">
+      <x:c r="J11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$12,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K11" s="40" t="n">
+      <x:c r="K11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$12,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L11" s="40" t="n">
+      <x:c r="L11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$12,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M11" s="40" t="n">
+      <x:c r="M11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$E$7:$E$12,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="22" customHeight="1">
-      <x:c r="A12" s="35" t="str">
+      <x:c r="A12" s="33" t="str">
         <x:v>Espèces et factions</x:v>
       </x:c>
-      <x:c r="B12" s="39" t="n">
+      <x:c r="B12" s="37" t="n">
         <x:f>COUNTA('Especes_factions'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C12" s="39" t="n">
+      <x:c r="C12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$8,"Défini")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D12" s="37" t="n">
+        <x:f>COUNTIFS('Especes_factions'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D12" s="39" t="n">
-        <x:f>COUNTIFS('Especes_factions'!$C$7:$C$8,"Prototype")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E12" s="39" t="n">
+      <x:c r="E12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F12" s="39" t="n">
+      <x:c r="F12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G12" s="39" t="n">
+      <x:c r="G12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$8,"Établi")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H12" s="39" t="n">
+      <x:c r="H12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I12" s="39" t="n">
+      <x:c r="I12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J12" s="39" t="n">
+      <x:c r="J12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K12" s="39" t="n">
+      <x:c r="K12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L12" s="39" t="n">
+      <x:c r="L12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M12" s="39" t="n">
+      <x:c r="M12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2438,104 +2432,104 @@
       <x:c r="A13" s="2" t="str">
         <x:v>Mondes</x:v>
       </x:c>
-      <x:c r="B13" s="40" t="n">
+      <x:c r="B13" s="38" t="n">
         <x:f>COUNTA('Mondes'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C13" s="40" t="n">
+      <x:c r="C13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$9,"Défini")</x:f>
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D13" s="40" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$9,"Prototype")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E13" s="40" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F13" s="40" t="n">
+      <x:c r="F13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G13" s="40" t="n">
+      <x:c r="G13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$9,"Établi")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H13" s="40" t="n">
+      <x:c r="H13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I13" s="40" t="n">
+      <x:c r="I13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J13" s="40" t="n">
+      <x:c r="J13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K13" s="40" t="n">
+      <x:c r="K13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L13" s="40" t="n">
+      <x:c r="L13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M13" s="40" t="n">
+      <x:c r="M13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="22" customHeight="1">
-      <x:c r="A14" s="35" t="str">
+      <x:c r="A14" s="33" t="str">
         <x:v>Zones</x:v>
       </x:c>
-      <x:c r="B14" s="39" t="n">
+      <x:c r="B14" s="37" t="n">
         <x:f>COUNTA('Zones'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C14" s="39" t="n">
+      <x:c r="C14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D14" s="39" t="n">
+      <x:c r="D14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E14" s="39" t="n">
+      <x:c r="E14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F14" s="39" t="n">
+      <x:c r="F14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G14" s="39" t="n">
+      <x:c r="G14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H14" s="39" t="n">
+      <x:c r="H14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I14" s="39" t="n">
+      <x:c r="I14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J14" s="39" t="n">
+      <x:c r="J14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K14" s="39" t="n">
+      <x:c r="K14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L14" s="39" t="n">
+      <x:c r="L14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M14" s="39" t="n">
+      <x:c r="M14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2544,104 +2538,104 @@
       <x:c r="A15" s="2" t="str">
         <x:v>Liaisons</x:v>
       </x:c>
-      <x:c r="B15" s="40" t="n">
+      <x:c r="B15" s="38" t="n">
         <x:f>COUNTA('Liaisons'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C15" s="40" t="n">
+      <x:c r="C15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D15" s="40" t="n">
+      <x:c r="D15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E15" s="40" t="n">
+      <x:c r="E15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F15" s="40" t="n">
+      <x:c r="F15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G15" s="40" t="n">
+      <x:c r="G15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H15" s="40" t="n">
+      <x:c r="H15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I15" s="40" t="n">
+      <x:c r="I15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J15" s="40" t="n">
+      <x:c r="J15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K15" s="40" t="n">
+      <x:c r="K15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L15" s="40" t="n">
+      <x:c r="L15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M15" s="40" t="n">
+      <x:c r="M15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="22" customHeight="1">
-      <x:c r="A16" s="35" t="str">
+      <x:c r="A16" s="33" t="str">
         <x:v>Décors</x:v>
       </x:c>
-      <x:c r="B16" s="39" t="n">
+      <x:c r="B16" s="37" t="n">
         <x:f>COUNTA('Decors'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C16" s="39" t="n">
+      <x:c r="C16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D16" s="39" t="n">
+      <x:c r="D16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E16" s="39" t="n">
+      <x:c r="E16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F16" s="39" t="n">
+      <x:c r="F16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G16" s="39" t="n">
+      <x:c r="G16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H16" s="39" t="n">
+      <x:c r="H16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I16" s="39" t="n">
+      <x:c r="I16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J16" s="39" t="n">
+      <x:c r="J16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K16" s="39" t="n">
+      <x:c r="K16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L16" s="39" t="n">
+      <x:c r="L16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M16" s="39" t="n">
+      <x:c r="M16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2650,104 +2644,104 @@
       <x:c r="A17" s="2" t="str">
         <x:v>Props</x:v>
       </x:c>
-      <x:c r="B17" s="40" t="n">
+      <x:c r="B17" s="38" t="n">
         <x:f>COUNTA('Props'!$A$7:$A$7)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C17" s="40" t="n">
+      <x:c r="C17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$7,"Défini")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D17" s="40" t="n">
+      <x:c r="D17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E17" s="40" t="n">
+      <x:c r="E17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F17" s="40" t="n">
+      <x:c r="F17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G17" s="40" t="n">
+      <x:c r="G17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$7,"Établi")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H17" s="40" t="n">
+      <x:c r="H17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I17" s="40" t="n">
+      <x:c r="I17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J17" s="40" t="n">
+      <x:c r="J17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K17" s="40" t="n">
+      <x:c r="K17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L17" s="40" t="n">
+      <x:c r="L17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M17" s="40" t="n">
+      <x:c r="M17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="22" customHeight="1">
-      <x:c r="A18" s="35" t="str">
+      <x:c r="A18" s="33" t="str">
         <x:v>Ennemis et boss</x:v>
       </x:c>
-      <x:c r="B18" s="39" t="n">
+      <x:c r="B18" s="37" t="n">
         <x:f>COUNTA('Ennemis_boss'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C18" s="39" t="n">
+      <x:c r="C18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D18" s="39" t="n">
+      <x:c r="D18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E18" s="39" t="n">
+      <x:c r="E18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F18" s="39" t="n">
+      <x:c r="F18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G18" s="39" t="n">
+      <x:c r="G18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H18" s="39" t="n">
+      <x:c r="H18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I18" s="39" t="n">
+      <x:c r="I18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J18" s="39" t="n">
+      <x:c r="J18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K18" s="39" t="n">
+      <x:c r="K18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L18" s="39" t="n">
+      <x:c r="L18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M18" s="39" t="n">
+      <x:c r="M18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2756,104 +2750,104 @@
       <x:c r="A19" s="2" t="str">
         <x:v>Missions</x:v>
       </x:c>
-      <x:c r="B19" s="40" t="n">
+      <x:c r="B19" s="38" t="n">
         <x:f>COUNTA('Missions'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C19" s="40" t="n">
+      <x:c r="C19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D19" s="40" t="n">
+      <x:c r="D19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E19" s="40" t="n">
+      <x:c r="E19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F19" s="40" t="n">
+      <x:c r="F19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G19" s="40" t="n">
+      <x:c r="G19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H19" s="40" t="n">
+      <x:c r="H19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I19" s="40" t="n">
+      <x:c r="I19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J19" s="40" t="n">
+      <x:c r="J19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K19" s="40" t="n">
+      <x:c r="K19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L19" s="40" t="n">
+      <x:c r="L19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M19" s="40" t="n">
+      <x:c r="M19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$E$7:$E$14,"P0")</x:f>
         <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="22" customHeight="1">
-      <x:c r="A20" s="35" t="str">
+      <x:c r="A20" s="33" t="str">
         <x:v>Secondaires et DLC</x:v>
       </x:c>
-      <x:c r="B20" s="39" t="n">
+      <x:c r="B20" s="37" t="n">
         <x:f>COUNTA('Secondaires_DLC'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C20" s="39" t="n">
+      <x:c r="C20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D20" s="39" t="n">
+      <x:c r="D20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E20" s="39" t="n">
+      <x:c r="E20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F20" s="39" t="n">
+      <x:c r="F20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G20" s="39" t="n">
+      <x:c r="G20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H20" s="39" t="n">
+      <x:c r="H20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I20" s="39" t="n">
+      <x:c r="I20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J20" s="39" t="n">
+      <x:c r="J20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K20" s="39" t="n">
+      <x:c r="K20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L20" s="39" t="n">
+      <x:c r="L20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M20" s="39" t="n">
+      <x:c r="M20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2862,104 +2856,104 @@
       <x:c r="A21" s="2" t="str">
         <x:v>Choix et relations</x:v>
       </x:c>
-      <x:c r="B21" s="40" t="n">
+      <x:c r="B21" s="38" t="n">
         <x:f>COUNTA('Choix_relations'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C21" s="40" t="n">
+      <x:c r="C21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D21" s="40" t="n">
+      <x:c r="D21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E21" s="40" t="n">
+      <x:c r="E21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F21" s="40" t="n">
+      <x:c r="F21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G21" s="40" t="n">
+      <x:c r="G21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H21" s="40" t="n">
+      <x:c r="H21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I21" s="40" t="n">
+      <x:c r="I21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J21" s="40" t="n">
+      <x:c r="J21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K21" s="40" t="n">
+      <x:c r="K21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L21" s="40" t="n">
+      <x:c r="L21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M21" s="40" t="n">
+      <x:c r="M21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="22" customHeight="1">
-      <x:c r="A22" s="35" t="str">
+      <x:c r="A22" s="33" t="str">
         <x:v>Dialogues</x:v>
       </x:c>
-      <x:c r="B22" s="39" t="n">
+      <x:c r="B22" s="37" t="n">
         <x:f>COUNTA('Dialogues'!$A$7:$A$16)</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C22" s="39" t="n">
+      <x:c r="C22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$16,"Défini")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D22" s="39" t="n">
+      <x:c r="D22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$16,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E22" s="39" t="n">
+      <x:c r="E22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$16,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F22" s="39" t="n">
+      <x:c r="F22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$16,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G22" s="39" t="n">
+      <x:c r="G22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$16,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H22" s="39" t="n">
+      <x:c r="H22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$16,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I22" s="39" t="n">
+      <x:c r="I22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$16,"Extrapolation")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J22" s="39" t="n">
+      <x:c r="J22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$16,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K22" s="39" t="n">
+      <x:c r="K22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$16,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L22" s="39" t="n">
+      <x:c r="L22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$16,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M22" s="39" t="n">
+      <x:c r="M22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$E$7:$E$16,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2968,104 +2962,104 @@
       <x:c r="A23" s="2" t="str">
         <x:v>Cinématiques</x:v>
       </x:c>
-      <x:c r="B23" s="40" t="n">
+      <x:c r="B23" s="38" t="n">
         <x:f>COUNTA('Cinematiques'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C23" s="40" t="n">
+      <x:c r="C23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D23" s="40" t="n">
+      <x:c r="D23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E23" s="40" t="n">
+      <x:c r="E23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F23" s="40" t="n">
+      <x:c r="F23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G23" s="40" t="n">
+      <x:c r="G23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H23" s="40" t="n">
+      <x:c r="H23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I23" s="40" t="n">
+      <x:c r="I23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J23" s="40" t="n">
+      <x:c r="J23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K23" s="40" t="n">
+      <x:c r="K23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L23" s="40" t="n">
+      <x:c r="L23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M23" s="40" t="n">
+      <x:c r="M23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="22" customHeight="1">
-      <x:c r="A24" s="35" t="str">
+      <x:c r="A24" s="33" t="str">
         <x:v>Armes</x:v>
       </x:c>
-      <x:c r="B24" s="39" t="n">
+      <x:c r="B24" s="37" t="n">
         <x:f>COUNTA('Armes'!$A$7:$A$7)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C24" s="39" t="n">
+      <x:c r="C24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Défini")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D24" s="39" t="n">
+      <x:c r="D24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E24" s="39" t="n">
+      <x:c r="E24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F24" s="39" t="n">
+      <x:c r="F24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G24" s="39" t="n">
+      <x:c r="G24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Établi")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H24" s="39" t="n">
+      <x:c r="H24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I24" s="39" t="n">
+      <x:c r="I24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J24" s="39" t="n">
+      <x:c r="J24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K24" s="39" t="n">
+      <x:c r="K24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L24" s="39" t="n">
+      <x:c r="L24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M24" s="39" t="n">
+      <x:c r="M24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3074,104 +3068,104 @@
       <x:c r="A25" s="2" t="str">
         <x:v>Armures et équipement</x:v>
       </x:c>
-      <x:c r="B25" s="40" t="n">
+      <x:c r="B25" s="38" t="n">
         <x:f>COUNTA('Armures_equipement'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C25" s="40" t="n">
+      <x:c r="C25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$9,"Défini")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D25" s="40" t="n">
+      <x:c r="D25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$9,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E25" s="40" t="n">
+      <x:c r="E25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F25" s="40" t="n">
+      <x:c r="F25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G25" s="40" t="n">
+      <x:c r="G25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$9,"Établi")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H25" s="40" t="n">
+      <x:c r="H25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I25" s="40" t="n">
+      <x:c r="I25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J25" s="40" t="n">
+      <x:c r="J25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K25" s="40" t="n">
+      <x:c r="K25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L25" s="40" t="n">
+      <x:c r="L25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M25" s="40" t="n">
+      <x:c r="M25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="22" customHeight="1">
-      <x:c r="A26" s="35" t="str">
+      <x:c r="A26" s="33" t="str">
         <x:v>Pouvoirs</x:v>
       </x:c>
-      <x:c r="B26" s="39" t="n">
+      <x:c r="B26" s="37" t="n">
         <x:f>COUNTA('Pouvoirs'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C26" s="39" t="n">
+      <x:c r="C26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D26" s="39" t="n">
+      <x:c r="D26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E26" s="39" t="n">
+      <x:c r="E26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F26" s="39" t="n">
+      <x:c r="F26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G26" s="39" t="n">
+      <x:c r="G26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$8,"Établi")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H26" s="39" t="n">
+      <x:c r="H26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I26" s="39" t="n">
+      <x:c r="I26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J26" s="39" t="n">
+      <x:c r="J26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K26" s="39" t="n">
+      <x:c r="K26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L26" s="39" t="n">
+      <x:c r="L26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M26" s="39" t="n">
+      <x:c r="M26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3180,104 +3174,104 @@
       <x:c r="A27" s="2" t="str">
         <x:v>Movesets alliés</x:v>
       </x:c>
-      <x:c r="B27" s="40" t="n">
+      <x:c r="B27" s="38" t="n">
         <x:f>COUNTA('Movesets_allies'!$A$7:$A$12)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C27" s="40" t="n">
+      <x:c r="C27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$12,"Défini")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D27" s="40" t="n">
+      <x:c r="D27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$12,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E27" s="40" t="n">
+      <x:c r="E27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$12,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F27" s="40" t="n">
+      <x:c r="F27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$12,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G27" s="40" t="n">
+      <x:c r="G27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$12,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H27" s="40" t="n">
+      <x:c r="H27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$12,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I27" s="40" t="n">
+      <x:c r="I27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$12,"Extrapolation")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="J27" s="40" t="n">
+      <x:c r="J27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$12,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K27" s="40" t="n">
+      <x:c r="K27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$12,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L27" s="40" t="n">
+      <x:c r="L27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$12,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M27" s="40" t="n">
+      <x:c r="M27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$E$7:$E$12,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="22" customHeight="1">
-      <x:c r="A28" s="35" t="str">
+      <x:c r="A28" s="33" t="str">
         <x:v>Movesets ennemis</x:v>
       </x:c>
-      <x:c r="B28" s="39" t="n">
+      <x:c r="B28" s="37" t="n">
         <x:f>COUNTA('Movesets_ennemis'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C28" s="39" t="n">
+      <x:c r="C28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D28" s="39" t="n">
+      <x:c r="D28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E28" s="39" t="n">
+      <x:c r="E28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F28" s="39" t="n">
+      <x:c r="F28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G28" s="39" t="n">
+      <x:c r="G28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H28" s="39" t="n">
+      <x:c r="H28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I28" s="39" t="n">
+      <x:c r="I28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J28" s="39" t="n">
+      <x:c r="J28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K28" s="39" t="n">
+      <x:c r="K28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L28" s="39" t="n">
+      <x:c r="L28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M28" s="39" t="n">
+      <x:c r="M28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3286,104 +3280,104 @@
       <x:c r="A29" s="2" t="str">
         <x:v>Animations</x:v>
       </x:c>
-      <x:c r="B29" s="40" t="n">
+      <x:c r="B29" s="38" t="n">
         <x:f>COUNTA('Animations'!$A$7:$A$16)</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C29" s="40" t="n">
+      <x:c r="C29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$16,"Défini")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D29" s="40" t="n">
+      <x:c r="D29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$16,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E29" s="40" t="n">
+      <x:c r="E29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$16,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F29" s="40" t="n">
+      <x:c r="F29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$16,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G29" s="40" t="n">
+      <x:c r="G29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H29" s="40" t="n">
+      <x:c r="H29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I29" s="40" t="n">
+      <x:c r="I29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"Extrapolation")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J29" s="40" t="n">
+      <x:c r="J29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K29" s="40" t="n">
+      <x:c r="K29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L29" s="40" t="n">
+      <x:c r="L29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M29" s="40" t="n">
+      <x:c r="M29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$E$7:$E$16,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="22" customHeight="1">
-      <x:c r="A30" s="35" t="str">
+      <x:c r="A30" s="33" t="str">
         <x:v>Sprites</x:v>
       </x:c>
-      <x:c r="B30" s="39" t="n">
+      <x:c r="B30" s="37" t="n">
         <x:f>COUNTA('Sprites'!$A$7:$A$16)</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C30" s="39" t="n">
+      <x:c r="C30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$16,"Défini")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D30" s="39" t="n">
+      <x:c r="D30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$16,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E30" s="39" t="n">
+      <x:c r="E30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$16,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F30" s="39" t="n">
+      <x:c r="F30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$16,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G30" s="39" t="n">
+      <x:c r="G30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H30" s="39" t="n">
+      <x:c r="H30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I30" s="39" t="n">
+      <x:c r="I30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"Extrapolation")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J30" s="39" t="n">
+      <x:c r="J30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K30" s="39" t="n">
+      <x:c r="K30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L30" s="39" t="n">
+      <x:c r="L30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M30" s="39" t="n">
+      <x:c r="M30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$E$7:$E$16,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3392,104 +3386,104 @@
       <x:c r="A31" s="2" t="str">
         <x:v>VFX</x:v>
       </x:c>
-      <x:c r="B31" s="40" t="n">
+      <x:c r="B31" s="38" t="n">
         <x:f>COUNTA('VFX'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C31" s="40" t="n">
+      <x:c r="C31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D31" s="40" t="n">
+      <x:c r="D31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E31" s="40" t="n">
+      <x:c r="E31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F31" s="40" t="n">
+      <x:c r="F31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G31" s="40" t="n">
+      <x:c r="G31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$10,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H31" s="40" t="n">
+      <x:c r="H31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I31" s="40" t="n">
+      <x:c r="I31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J31" s="40" t="n">
+      <x:c r="J31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K31" s="40" t="n">
+      <x:c r="K31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L31" s="40" t="n">
+      <x:c r="L31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M31" s="40" t="n">
+      <x:c r="M31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="22" customHeight="1">
-      <x:c r="A32" s="35" t="str">
+      <x:c r="A32" s="33" t="str">
         <x:v>Audio</x:v>
       </x:c>
-      <x:c r="B32" s="39" t="n">
+      <x:c r="B32" s="37" t="n">
         <x:f>COUNTA('Audio'!$A$7:$A$11)</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C32" s="39" t="n">
+      <x:c r="C32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$11,"Défini")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D32" s="39" t="n">
+      <x:c r="D32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$11,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E32" s="39" t="n">
+      <x:c r="E32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$11,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F32" s="39" t="n">
+      <x:c r="F32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$11,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G32" s="39" t="n">
+      <x:c r="G32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H32" s="39" t="n">
+      <x:c r="H32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I32" s="39" t="n">
+      <x:c r="I32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"Extrapolation")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="J32" s="39" t="n">
+      <x:c r="J32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K32" s="39" t="n">
+      <x:c r="K32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L32" s="39" t="n">
+      <x:c r="L32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M32" s="39" t="n">
+      <x:c r="M32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$E$7:$E$11,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3498,104 +3492,104 @@
       <x:c r="A33" s="2" t="str">
         <x:v>Systèmes et UI</x:v>
       </x:c>
-      <x:c r="B33" s="40" t="n">
+      <x:c r="B33" s="38" t="n">
         <x:f>COUNTA('UI_systemes'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C33" s="40" t="n">
+      <x:c r="C33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D33" s="40" t="n">
+      <x:c r="D33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E33" s="40" t="n">
+      <x:c r="E33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F33" s="40" t="n">
+      <x:c r="F33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G33" s="40" t="n">
+      <x:c r="G33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H33" s="40" t="n">
+      <x:c r="H33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I33" s="40" t="n">
+      <x:c r="I33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J33" s="40" t="n">
+      <x:c r="J33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K33" s="40" t="n">
+      <x:c r="K33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L33" s="40" t="n">
+      <x:c r="L33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M33" s="40" t="n">
+      <x:c r="M33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$E$7:$E$14,"P0")</x:f>
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="22" customHeight="1">
-      <x:c r="A34" s="35" t="str">
+      <x:c r="A34" s="33" t="str">
         <x:v>QA</x:v>
       </x:c>
-      <x:c r="B34" s="39" t="n">
+      <x:c r="B34" s="37" t="n">
         <x:f>COUNTA('QA'!$A$7:$A$18)</x:f>
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C34" s="39" t="n">
+      <x:c r="C34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$18,"Défini")</x:f>
         <x:v>12</x:v>
       </x:c>
-      <x:c r="D34" s="39" t="n">
+      <x:c r="D34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$18,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E34" s="39" t="n">
+      <x:c r="E34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$18,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F34" s="39" t="n">
+      <x:c r="F34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$18,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G34" s="39" t="n">
+      <x:c r="G34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$18,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H34" s="39" t="n">
+      <x:c r="H34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$18,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I34" s="39" t="n">
+      <x:c r="I34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$18,"Extrapolation")</x:f>
         <x:v>12</x:v>
       </x:c>
-      <x:c r="J34" s="39" t="n">
+      <x:c r="J34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$18,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K34" s="39" t="n">
+      <x:c r="K34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$18,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L34" s="39" t="n">
+      <x:c r="L34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$18,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M34" s="39" t="n">
+      <x:c r="M34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$E$7:$E$18,"P0")</x:f>
         <x:v>3</x:v>
       </x:c>
@@ -3604,119 +3598,119 @@
       <x:c r="A35" s="2" t="str">
         <x:v>Continuité</x:v>
       </x:c>
-      <x:c r="B35" s="40" t="n">
+      <x:c r="B35" s="38" t="n">
         <x:f>COUNTA('Continuite'!$A$7:$A$13)</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C35" s="40" t="n">
+      <x:c r="C35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$13,"Défini")</x:f>
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D35" s="40" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$13,"Prototype")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E35" s="40" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$13,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F35" s="40" t="n">
+      <x:c r="F35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$13,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G35" s="40" t="n">
+      <x:c r="G35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$13,"Établi")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H35" s="40" t="n">
+      <x:c r="H35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$13,"À vérifier")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I35" s="40" t="n">
+      <x:c r="I35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$13,"Extrapolation")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J35" s="40" t="n">
+      <x:c r="J35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$13,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K35" s="40" t="n">
+      <x:c r="K35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$13,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L35" s="40" t="n">
+      <x:c r="L35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$13,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M35" s="40" t="n">
+      <x:c r="M35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$E$7:$E$13,"P0")</x:f>
         <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="22" customHeight="1">
       <x:c r="A36" s="2"/>
-      <x:c r="B36" s="40"/>
-      <x:c r="C36" s="40"/>
-      <x:c r="D36" s="40"/>
-      <x:c r="E36" s="40"/>
-      <x:c r="F36" s="40"/>
-      <x:c r="G36" s="40"/>
-      <x:c r="H36" s="40"/>
-      <x:c r="I36" s="40"/>
-      <x:c r="J36" s="40"/>
-      <x:c r="K36" s="40"/>
-      <x:c r="L36" s="40"/>
-      <x:c r="M36" s="40"/>
+      <x:c r="B36" s="38"/>
+      <x:c r="C36" s="38"/>
+      <x:c r="D36" s="38"/>
+      <x:c r="E36" s="38"/>
+      <x:c r="F36" s="38"/>
+      <x:c r="G36" s="38"/>
+      <x:c r="H36" s="38"/>
+      <x:c r="I36" s="38"/>
+      <x:c r="J36" s="38"/>
+      <x:c r="K36" s="38"/>
+      <x:c r="L36" s="38"/>
+      <x:c r="M36" s="38"/>
     </x:row>
     <x:row r="37" ht="28" customHeight="1">
-      <x:c r="A37" s="23" t="str">
+      <x:c r="A37" s="21" t="str">
         <x:v>TOTAL</x:v>
       </x:c>
-      <x:c r="B37" s="41" t="n">
+      <x:c r="B37" s="39" t="n">
         <x:f>SUM(B10:B35)</x:f>
         <x:v>158</x:v>
       </x:c>
-      <x:c r="C37" s="41" t="n">
+      <x:c r="C37" s="39" t="n">
         <x:f>SUM(C10:C35)</x:f>
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="D37" s="41" t="n">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="D37" s="39" t="n">
         <x:f>SUM(D10:D35)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E37" s="41" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E37" s="39" t="n">
         <x:f>SUM(E10:E35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F37" s="41" t="n">
+      <x:c r="F37" s="39" t="n">
         <x:f>SUM(F10:F35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G37" s="41" t="n">
+      <x:c r="G37" s="39" t="n">
         <x:f>SUM(G10:G35)</x:f>
         <x:v>27</x:v>
       </x:c>
-      <x:c r="H37" s="41" t="n">
+      <x:c r="H37" s="39" t="n">
         <x:f>SUM(H10:H35)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I37" s="41" t="n">
+      <x:c r="I37" s="39" t="n">
         <x:f>SUM(I10:I35)</x:f>
         <x:v>130</x:v>
       </x:c>
-      <x:c r="J37" s="41" t="n">
+      <x:c r="J37" s="39" t="n">
         <x:f>SUM(J10:J35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K37" s="41" t="n">
+      <x:c r="K37" s="39" t="n">
         <x:f>SUM(K10:K35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L37" s="41" t="n">
+      <x:c r="L37" s="39" t="n">
         <x:f>SUM(L10:L35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M37" s="41" t="n">
+      <x:c r="M37" s="39" t="n">
         <x:f>SUM(M10:M35)</x:f>
         <x:v>20</x:v>
       </x:c>
@@ -3940,61 +3934,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -4044,8 +4038,8 @@
       <x:c r="O7" s="9" t="str"/>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str">
         <x:v>Tous comportements et réglages de combat sont du design original.</x:v>
       </x:c>
     </x:row>
@@ -4095,8 +4089,8 @@
       <x:c r="O8" s="7" t="str"/>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str">
         <x:v>Tous comportements et réglages de combat sont du design original.</x:v>
       </x:c>
     </x:row>
@@ -4146,8 +4140,8 @@
       <x:c r="O9" s="9" t="str"/>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str">
         <x:v>Tous comportements et réglages de combat sont du design original.</x:v>
       </x:c>
     </x:row>
@@ -4197,8 +4191,8 @@
       <x:c r="O10" s="7" t="str"/>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str">
         <x:v>Tous comportements et réglages de combat sont du design original.</x:v>
       </x:c>
     </x:row>
@@ -4234,7 +4228,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab72911dd8694da1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2eefa6f560f14a17"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4374,61 +4368,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -4480,8 +4474,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -4531,8 +4525,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -4582,8 +4576,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -4633,8 +4627,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -4684,8 +4678,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -4735,8 +4729,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="68" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -4786,8 +4780,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="68" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -4837,8 +4831,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -4872,7 +4866,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a0245856ba047ef"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdcc3c5b7edee4e72"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5012,61 +5006,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -5118,8 +5112,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -5169,8 +5163,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -5220,8 +5214,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -5271,8 +5265,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -5322,8 +5316,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -5373,8 +5367,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -5424,8 +5418,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -5475,8 +5469,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -5510,7 +5504,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79dfa6644756468f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5bc66dbde5c4a97"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5650,61 +5644,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -5756,8 +5750,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -5807,8 +5801,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -5858,8 +5852,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -5909,8 +5903,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -5960,8 +5954,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -6011,8 +6005,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -6062,8 +6056,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -6113,8 +6107,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -6148,7 +6142,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb6d35b2a68944415"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1501248c734443d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6288,61 +6282,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -6394,8 +6388,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6447,8 +6441,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6500,8 +6494,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6553,8 +6547,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6606,8 +6600,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6659,8 +6653,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6712,8 +6706,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6765,8 +6759,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str">
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6818,8 +6812,8 @@
       </x:c>
       <x:c r="P15" s="9" t="str"/>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str">
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6871,8 +6865,8 @@
       </x:c>
       <x:c r="P16" s="7" t="str"/>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str">
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6908,7 +6902,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R452a9dcda6e24fcf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4fa19654a0248f7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7048,61 +7042,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -7154,8 +7148,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -7205,8 +7199,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -7256,8 +7250,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -7307,8 +7301,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -7358,8 +7352,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -7409,8 +7403,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -7460,8 +7454,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -7511,8 +7505,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -7546,7 +7540,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0937baa0a5c4477"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R12c42006074c4cb7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7686,61 +7680,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -7786,10 +7780,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>ASC-SRC-HEN</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Hendel_Mitra</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -7825,7 +7819,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6054af1407864f94"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e34aa25f1bc48fe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7965,61 +7959,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -8065,10 +8059,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>ASC-SRC-IDENNA</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Idenna</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -8114,10 +8108,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>ASC-SRC-HILO</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Hilo%27Jaa_vas_Idenna</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -8163,10 +8157,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>ASC-SRC-GOLO</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Golo</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -8202,7 +8196,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70c7ef9897934752"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R90ea52645e014e41"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8342,61 +8336,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -8442,10 +8436,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>ASC-SRC-PUB</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/89888/mass-effect-ascension-by-drew-karpyshyn/paperback/</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -8491,10 +8485,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>ASC-SRC-HEN</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Hendel_Mitra</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -8530,7 +8524,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree69bdabe18d46d2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra9f08a33b3394d47"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8670,61 +8664,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -8774,8 +8768,8 @@
       <x:c r="O7" s="9" t="str"/>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -8823,8 +8817,8 @@
       <x:c r="O8" s="7" t="str"/>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -8872,8 +8866,8 @@
       <x:c r="O9" s="9" t="str"/>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -8921,8 +8915,8 @@
       <x:c r="O10" s="7" t="str"/>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -8970,8 +8964,8 @@
       <x:c r="O11" s="9" t="str"/>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -9019,8 +9013,8 @@
       <x:c r="O12" s="7" t="str"/>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D12">
@@ -9054,7 +9048,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1ebb328f37347bd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf35482209cba4db6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9194,61 +9188,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -9294,10 +9288,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>ASC-SRC-PUB</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/89888/mass-effect-ascension-by-drew-karpyshyn/paperback/</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -9343,10 +9337,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>ASC-SRC-PUB</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/89888/mass-effect-ascension-by-drew-karpyshyn/paperback/</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -9392,10 +9386,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>ASC-SRC-HEN</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Hendel_Mitra</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -9441,10 +9435,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>ASC-SRC-LEMM</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Lemm%27Shal_nar_Tesleya</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -9480,7 +9474,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf93b31accc9a46f1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6070efe3fa644e0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9620,61 +9614,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -9726,8 +9720,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -9777,8 +9771,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -9828,8 +9822,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -9879,8 +9873,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D10">
@@ -9914,7 +9908,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e50c2b58e124975"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R385f9410d9724231"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10054,61 +10048,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -10160,8 +10154,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -10211,8 +10205,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -10262,8 +10256,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -10313,8 +10307,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -10364,8 +10358,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -10415,8 +10409,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -10466,8 +10460,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -10517,8 +10511,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="54" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -10568,8 +10562,8 @@
       </x:c>
       <x:c r="P15" s="9" t="str"/>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
     <x:row r="16" ht="54" customHeight="1">
       <x:c r="A16" s="19" t="str">
@@ -10619,8 +10613,8 @@
       </x:c>
       <x:c r="P16" s="7" t="str"/>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str"/>
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D16">
@@ -10654,7 +10648,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70a0143eee0c461a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6665b05dccf54566"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10794,61 +10788,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -10900,8 +10894,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -10951,8 +10945,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -11002,8 +10996,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -11053,8 +11047,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -11104,8 +11098,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -11155,8 +11149,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -11206,8 +11200,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="68" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -11257,8 +11251,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="68" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -11308,8 +11302,8 @@
       </x:c>
       <x:c r="P15" s="9" t="str"/>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
     <x:row r="16" ht="68" customHeight="1">
       <x:c r="A16" s="19" t="str">
@@ -11359,8 +11353,8 @@
       </x:c>
       <x:c r="P16" s="7" t="str"/>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str"/>
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D16">
@@ -11394,7 +11388,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf877146665c14fe0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R144874bc233c48c6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11534,61 +11528,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -11640,8 +11634,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -11691,8 +11685,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -11742,8 +11736,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -11793,8 +11787,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D10">
@@ -11828,7 +11822,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff2554b6175b49b2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R478988a965e4477a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11968,61 +11962,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -12072,8 +12066,8 @@
       <x:c r="O7" s="9" t="str"/>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="82" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -12121,8 +12115,8 @@
       <x:c r="O8" s="7" t="str"/>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -12170,8 +12164,8 @@
       <x:c r="O9" s="9" t="str"/>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -12219,8 +12213,8 @@
       <x:c r="O10" s="7" t="str"/>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -12268,8 +12262,8 @@
       <x:c r="O11" s="9" t="str"/>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D11">
@@ -12303,7 +12297,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7b02cc71482401a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb9da72c007154453"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12443,61 +12437,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -12547,8 +12541,8 @@
       <x:c r="O7" s="9" t="str"/>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -12596,8 +12590,8 @@
       <x:c r="O8" s="7" t="str"/>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="44" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -12645,8 +12639,8 @@
       <x:c r="O9" s="9" t="str"/>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="44" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -12694,8 +12688,8 @@
       <x:c r="O10" s="7" t="str"/>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="44" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -12743,8 +12737,8 @@
       <x:c r="O11" s="9" t="str"/>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="44" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -12792,8 +12786,8 @@
       <x:c r="O12" s="7" t="str"/>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="44" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -12841,8 +12835,8 @@
       <x:c r="O13" s="9" t="str"/>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="44" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -12890,8 +12884,8 @@
       <x:c r="O14" s="7" t="str"/>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -12925,7 +12919,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe7111cfae9447e2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42ab31b60e524121"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13065,61 +13059,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -13171,8 +13165,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -13222,8 +13216,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -13273,8 +13267,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -13324,8 +13318,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -13375,8 +13369,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -13426,8 +13420,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -13477,8 +13471,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -13528,8 +13522,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="68" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -13571,8 +13565,8 @@
       <x:c r="O15" s="9" t="str"/>
       <x:c r="P15" s="9" t="str"/>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
     <x:row r="16" ht="68" customHeight="1">
       <x:c r="A16" s="19" t="str">
@@ -13614,8 +13608,8 @@
       <x:c r="O16" s="7" t="str"/>
       <x:c r="P16" s="7" t="str"/>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str"/>
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str"/>
     </x:row>
     <x:row r="17" ht="54" customHeight="1">
       <x:c r="A17" s="18" t="str">
@@ -13657,8 +13651,8 @@
       <x:c r="O17" s="9" t="str"/>
       <x:c r="P17" s="9" t="str"/>
       <x:c r="Q17" s="9" t="str"/>
-      <x:c r="R17" s="20" t="str"/>
-      <x:c r="S17" s="20" t="str"/>
+      <x:c r="R17" s="9" t="str"/>
+      <x:c r="S17" s="9" t="str"/>
     </x:row>
     <x:row r="18" ht="54" customHeight="1">
       <x:c r="A18" s="19" t="str">
@@ -13700,8 +13694,8 @@
       <x:c r="O18" s="7" t="str"/>
       <x:c r="P18" s="7" t="str"/>
       <x:c r="Q18" s="7" t="str"/>
-      <x:c r="R18" s="21" t="str"/>
-      <x:c r="S18" s="21" t="str"/>
+      <x:c r="R18" s="7" t="str"/>
+      <x:c r="S18" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D18">
@@ -13735,7 +13729,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R273b24ad50f94200"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf86284fc681d4072"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13762,7 +13756,7 @@
     <x:col min="16" max="16" width="45" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="24" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="89" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="73" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="255" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
@@ -13875,61 +13869,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -13975,10 +13969,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>ASC-SRC-PUB</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/89888/mass-effect-ascension-by-drew-karpyshyn/paperback/</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -14024,10 +14018,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>ASC-SRC-HEN</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Hendel_Mitra</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -14073,10 +14067,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>ASC-SRC-GIL</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Gillian_Grayson</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -14122,10 +14116,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>ASC-SRC-GIL</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Gillian_Grayson</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -14169,8 +14163,8 @@
         <x:v>Limite de continuité / contrôle transversal</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -14214,12 +14208,12 @@
         <x:v>Limite de continuité / contrôle transversal</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="68" customHeight="1">
+    <x:row r="13" ht="82" customHeight="1">
       <x:c r="A13" s="18" t="str">
         <x:v>ASC-CON-07</x:v>
       </x:c>
@@ -14227,7 +14221,7 @@
         <x:v>Retour et exploration</x:v>
       </x:c>
       <x:c r="C13" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D13" s="16" t="str">
         <x:v>Établi</x:v>
@@ -14246,7 +14240,7 @@
       <x:c r="J13" s="9" t="str"/>
       <x:c r="K13" s="9" t="str"/>
       <x:c r="L13" s="9" t="str">
-        <x:v>continuity/asc.json ; règle documentée et décision de validation datée.</x:v>
+        <x:v>Référence documentaire ASC-CON-07 consultable dans les lectures de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ou incarnation de personnage n’est produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M13" s="9" t="str">
         <x:v>Préserver Gillian comme personne et enfant dans le contexte d’Ascension ; les options de gameplay ne changent ni son identité ni les événements qui conduisent à son séjour sur l’Idenna.</x:v>
@@ -14261,11 +14255,11 @@
       <x:c r="Q13" s="9" t="str">
         <x:v>ASC-SRC-LEMM</x:v>
       </x:c>
-      <x:c r="R13" s="20" t="str">
+      <x:c r="R13" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Lemm%27Shal_nar_Tesleya</x:v>
       </x:c>
-      <x:c r="S13" s="20" t="str">
-        <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
+      <x:c r="S13" s="9" t="str">
+        <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié. Prototype limité à une paraphrase documentaire sourcée et aux références visitées. Les autres livrables de l’œuvre restent à produire ; les personnages mentionnés ne sont pas recrutables et les lieux cités ne deviennent pas des niveaux.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -14300,7 +14294,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93d84ac236aa449c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f19374a92424a34"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14365,10 +14359,10 @@
       <x:c r="F5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Champ</x:v>
       </x:c>
-      <x:c r="B6" s="32" t="str">
+      <x:c r="B6" s="30" t="str">
         <x:v>Définition</x:v>
       </x:c>
       <x:c r="C6" s="2"/>
@@ -14417,7 +14411,7 @@
         <x:v>Projet</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
-        <x:v>Projet Ascension, Gillian, Kahlee, Grayson, Cerberus et refuge quarien ; huit espaces proposés privilégiant enquête, confiance et protection.</x:v>
+        <x:v>158 fiches de production ; 4 fiches au stade Prototype de portée partielle. Les autres livrables restent des spécifications ; aucun achèvement intégral 1:1 revendiqué.</x:v>
       </x:c>
       <x:c r="C10" s="2"/>
       <x:c r="D10" s="2"/>
@@ -14436,11 +14430,11 @@
       <x:c r="E11" s="2"/>
       <x:c r="F11" s="2"/>
     </x:row>
-    <x:row r="12" ht="40" customHeight="1">
+    <x:row r="12" ht="30" customHeight="1">
       <x:c r="A12" s="7" t="str">
         <x:v>Date de référence</x:v>
       </x:c>
-      <x:c r="B12" s="44" t="d">
+      <x:c r="B12" s="42" t="d">
         <x:v>2026-10-22T12:00:00.000Z</x:v>
       </x:c>
       <x:c r="C12" s="2"/>
@@ -14593,22 +14587,22 @@
       <x:c r="F25" s="2"/>
     </x:row>
     <x:row r="26" ht="34" customHeight="1">
-      <x:c r="A26" s="30" t="str">
+      <x:c r="A26" s="28" t="str">
         <x:v>Source</x:v>
       </x:c>
-      <x:c r="B26" s="31" t="str">
+      <x:c r="B26" s="29" t="str">
         <x:v>Titre</x:v>
       </x:c>
-      <x:c r="C26" s="31" t="str">
+      <x:c r="C26" s="29" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="D26" s="31" t="str">
+      <x:c r="D26" s="29" t="str">
         <x:v>URL</x:v>
       </x:c>
-      <x:c r="E26" s="31" t="str">
+      <x:c r="E26" s="29" t="str">
         <x:v>Périmètre</x:v>
       </x:c>
-      <x:c r="F26" s="32" t="str">
+      <x:c r="F26" s="30" t="str">
         <x:v>Accès et limites</x:v>
       </x:c>
     </x:row>
@@ -14857,13 +14851,13 @@
       <x:c r="F40" s="2"/>
     </x:row>
     <x:row r="41" ht="34" customHeight="1">
-      <x:c r="A41" s="30" t="str">
+      <x:c r="A41" s="28" t="str">
         <x:v>Domaine</x:v>
       </x:c>
-      <x:c r="B41" s="31" t="str">
+      <x:c r="B41" s="29" t="str">
         <x:v>Couverture actuelle</x:v>
       </x:c>
-      <x:c r="C41" s="32" t="str">
+      <x:c r="C41" s="30" t="str">
         <x:v>Travail restant</x:v>
       </x:c>
       <x:c r="D41" s="2"/>
@@ -14940,10 +14934,16 @@
       <x:c r="E46" s="2"/>
       <x:c r="F46" s="2"/>
     </x:row>
-    <x:row r="47" ht="22" customHeight="1">
-      <x:c r="A47" s="2"/>
-      <x:c r="B47" s="2"/>
-      <x:c r="C47" s="2"/>
+    <x:row r="47" ht="96" customHeight="1">
+      <x:c r="A47" s="6" t="str">
+        <x:v>Complément pouvoirs, modules et lectures</x:v>
+      </x:c>
+      <x:c r="B47" s="6" t="str">
+        <x:v>0 fiches de pouvoirs utilisées, 0 familles de modules préparables et 4 références consultables dans une lecture documentaire. Les chemins et preuves sont inscrits sur les seules lignes Prototype.</x:v>
+      </x:c>
+      <x:c r="C47" s="6" t="str">
+        <x:v>Arbres et progression complets, modèles et rangs exacts, campagnes et dialogues intégraux, niveaux et ressources visuelles propres à l’œuvre restent à réaliser ou vérifier. Les références lues ne rendent pas leurs personnages jouables.</x:v>
+      </x:c>
       <x:c r="D47" s="2"/>
       <x:c r="E47" s="2"/>
       <x:c r="F47" s="2"/>
@@ -15499,6 +15499,14 @@
       <x:c r="D116" s="2"/>
       <x:c r="E116" s="2"/>
       <x:c r="F116" s="2"/>
+    </x:row>
+    <x:row r="117" ht="22" customHeight="1">
+      <x:c r="A117" s="2"/>
+      <x:c r="B117" s="2"/>
+      <x:c r="C117" s="2"/>
+      <x:c r="D117" s="2"/>
+      <x:c r="E117" s="2"/>
+      <x:c r="F117" s="2"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15640,61 +15648,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -15740,10 +15748,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>ASC-SRC-GIL</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Gillian_Grayson</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -15789,10 +15797,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>ASC-SRC-GOLO</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Golo</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -15838,10 +15846,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>ASC-SRC-HEN</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Hendel_Mitra</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -15887,10 +15895,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>ASC-SRC-HEN</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Hendel_Mitra</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -15936,10 +15944,10 @@
       <x:c r="Q11" s="9" t="str">
         <x:v>ASC-SRC-NICK</x:v>
       </x:c>
-      <x:c r="R11" s="20" t="str">
+      <x:c r="R11" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Nick_Donahue</x:v>
       </x:c>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="S11" s="9" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -15985,10 +15993,10 @@
       <x:c r="Q12" s="7" t="str">
         <x:v>ASC-SRC-MAL</x:v>
       </x:c>
-      <x:c r="R12" s="21" t="str">
+      <x:c r="R12" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Ysin%27Mal_vas_Idenna</x:v>
       </x:c>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="S12" s="7" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -16024,7 +16032,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3dddfb61981243d5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d879fcae207432e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16051,7 +16059,7 @@
     <x:col min="16" max="16" width="45" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="24" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="89" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="73" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="255" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
@@ -16164,65 +16172,65 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="68" customHeight="1">
+    <x:row r="7" ht="82" customHeight="1">
       <x:c r="A7" s="18" t="str">
         <x:v>ASC-REF-FLEET</x:v>
       </x:c>
@@ -16230,7 +16238,7 @@
         <x:v>Flotte nomade</x:v>
       </x:c>
       <x:c r="C7" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D7" s="16" t="str">
         <x:v>Établi</x:v>
@@ -16249,7 +16257,7 @@
       <x:c r="J7" s="9" t="str"/>
       <x:c r="K7" s="9" t="str"/>
       <x:c r="L7" s="9" t="str">
-        <x:v>Codex ref.asc.fleet ; affichage bref avec source.</x:v>
+        <x:v>Référence documentaire ASC-REF-FLEET consultable dans les lectures de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ou incarnation de personnage n’est produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M7" s="9" t="str">
         <x:v>Préserver Gillian comme personne et enfant dans le contexte d’Ascension ; les options de gameplay ne changent ni son identité ni les événements qui conduisent à son séjour sur l’Idenna.</x:v>
@@ -16264,14 +16272,14 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>ASC-SRC-HEN</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Hendel_Mitra</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
-        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="68" customHeight="1">
+      <x:c r="S7" s="9" t="str">
+        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène. Prototype limité à une paraphrase documentaire sourcée et aux références visitées. Les autres livrables de l’œuvre restent à produire ; les personnages mentionnés ne sont pas recrutables et les lieux cités ne deviennent pas des niveaux.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="82" customHeight="1">
       <x:c r="A8" s="19" t="str">
         <x:v>ASC-REF-CERBERUS</x:v>
       </x:c>
@@ -16279,7 +16287,7 @@
         <x:v>Cerberus</x:v>
       </x:c>
       <x:c r="C8" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D8" s="17" t="str">
         <x:v>Établi</x:v>
@@ -16298,7 +16306,7 @@
       <x:c r="J8" s="7" t="str"/>
       <x:c r="K8" s="7" t="str"/>
       <x:c r="L8" s="7" t="str">
-        <x:v>Codex ref.asc.cerberus ; affichage bref avec source.</x:v>
+        <x:v>Référence documentaire ASC-REF-CERBERUS consultable dans les lectures de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ou incarnation de personnage n’est produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M8" s="7" t="str">
         <x:v>Préserver Gillian comme personne et enfant dans le contexte d’Ascension ; les options de gameplay ne changent ni son identité ni les événements qui conduisent à son séjour sur l’Idenna.</x:v>
@@ -16313,11 +16321,11 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>ASC-SRC-PUB</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/89888/mass-effect-ascension-by-drew-karpyshyn/paperback/</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
-        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
+      <x:c r="S8" s="7" t="str">
+        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène. Prototype limité à une paraphrase documentaire sourcée et aux références visitées. Les autres livrables de l’œuvre restent à produire ; les personnages mentionnés ne sont pas recrutables et les lieux cités ne deviennent pas des niveaux.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -16352,7 +16360,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39f468dadd5a4f01"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00f821d96c4944a1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16379,7 +16387,7 @@
     <x:col min="16" max="16" width="45" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="24" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="69" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="73" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="255" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
@@ -16492,65 +16500,65 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="68" customHeight="1">
+    <x:row r="7" ht="82" customHeight="1">
       <x:c r="A7" s="18" t="str">
         <x:v>ASC-REF-ACADEMY</x:v>
       </x:c>
@@ -16558,7 +16566,7 @@
         <x:v>Académie Grissom</x:v>
       </x:c>
       <x:c r="C7" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D7" s="16" t="str">
         <x:v>Établi</x:v>
@@ -16577,7 +16585,7 @@
       <x:c r="J7" s="9" t="str"/>
       <x:c r="K7" s="9" t="str"/>
       <x:c r="L7" s="9" t="str">
-        <x:v>Codex ref.asc.academy ; affichage bref avec source.</x:v>
+        <x:v>Référence documentaire ASC-REF-ACADEMY consultable dans les lectures de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ou incarnation de personnage n’est produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M7" s="9" t="str">
         <x:v>Préserver Gillian comme personne et enfant dans le contexte d’Ascension ; les options de gameplay ne changent ni son identité ni les événements qui conduisent à son séjour sur l’Idenna.</x:v>
@@ -16592,11 +16600,11 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>ASC-SRC-GIL</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Gillian_Grayson</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
-        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
+      <x:c r="S7" s="9" t="str">
+        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène. Prototype limité à une paraphrase documentaire sourcée et aux références visitées. Les autres livrables de l’œuvre restent à produire ; les personnages mentionnés ne sont pas recrutables et les lieux cités ne deviennent pas des niveaux.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
@@ -16641,10 +16649,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>ASC-SRC-HEN</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Hendel_Mitra</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -16690,10 +16698,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>ASC-SRC-HILO</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Hilo%27Jaa_vas_Idenna</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -16729,7 +16737,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3700c215ee944599"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd727b5359a3a4587"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16869,61 +16877,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -16973,8 +16981,8 @@
       <x:c r="O7" s="9" t="str"/>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17024,8 +17032,8 @@
       <x:c r="O8" s="7" t="str"/>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17075,8 +17083,8 @@
       <x:c r="O9" s="9" t="str"/>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17126,8 +17134,8 @@
       <x:c r="O10" s="7" t="str"/>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17177,8 +17185,8 @@
       <x:c r="O11" s="9" t="str"/>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17228,8 +17236,8 @@
       <x:c r="O12" s="7" t="str"/>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17279,8 +17287,8 @@
       <x:c r="O13" s="9" t="str"/>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17330,8 +17338,8 @@
       <x:c r="O14" s="7" t="str"/>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str">
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17367,7 +17375,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R249884d4d0fb4ad4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra5f884221a8e4287"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17507,61 +17515,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -17613,8 +17621,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17666,8 +17674,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17719,8 +17727,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17772,8 +17780,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17825,8 +17833,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17878,8 +17886,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17931,8 +17939,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17984,8 +17992,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str">
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -18021,7 +18029,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R788e157ac16947df"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re751602224694c84"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18161,61 +18169,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -18267,8 +18275,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -18318,8 +18326,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -18369,8 +18377,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -18420,8 +18428,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -18471,8 +18479,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -18522,8 +18530,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -18573,8 +18581,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -18624,8 +18632,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -18659,7 +18667,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R605b8365cc9942fe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R33ae8f65555d43ac"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18799,61 +18807,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -18899,10 +18907,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>ASC-SRC-GOLO</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Golo</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -18938,7 +18946,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7401de6965b4004"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R324eac1baa7346e6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Ascension_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Ascension_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R591cc6c6757d4d33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Rc6e29e017c93495e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Rd5aa78169adb411a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R71a9591cf8964285"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Rc122590ae5174f90"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R801db173fd894f3c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R31cc87e4be38485a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R119558121f4541cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Rfb879c04cbbc4ea7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R99f886d4784f4ee3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R55e3ad83afb74948"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Rcd7d57af832c4494"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R6df3a89a8a874536"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R2768e26d88c44ee5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="Rd128d87afafb4ff2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R9be976f04f314295"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R4dda7d0678f94359"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Re4b1d8c1397b4bea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R7f238102c76d48ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R812475d7669f45c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Rcf8195d0663a4a09"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="Rfdc4107584844be0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Rf170844071224af6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R09cc52cc2f0d49c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R2eabe604dc414640"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R491e2f6f0153485d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Rd53bfb7b3eec4d4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R35a63a3fe3fd471c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Red9224dfd54b449c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R8d178b4739a648d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R23bf7050dcab4bc9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R892414026212457e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R672222205a60419c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R7847de510ae14f8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R3671dc483f964e2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Rab90b7272b1c4de3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R9c8b9aa01e0b4acc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="Rf0015377e6e3454b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Rfb56fe9869e94693"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R1fe181a7afec4c71"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R5ffe54f98b404ff6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R0d8d8490d8b2432e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R64ff6caea5554430"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R6bd0e8ac2a0a48a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="Rd3856b94ef86474a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R2221a7f776eb4595"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R848da0d2ab7a4c55"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Rc7c2e2f9f3a643e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R454eb6a8102449bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="Ra609b4e9b31f49d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R0560a8d589724a3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R8348605e1ef0487e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="Reded0d6c834d4f26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Reb54ec9de5e045d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R30cf1999e3c64ca1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="Rca9970c2d63248b6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4228,7 +4228,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2eefa6f560f14a17"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1de341eee8594898"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4866,7 +4866,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdcc3c5b7edee4e72"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4bd8c29c13214cb1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5504,7 +5504,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5bc66dbde5c4a97"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R90718b1a17f44258"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6142,7 +6142,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1501248c734443d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc7f3382ad58a438f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6902,7 +6902,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4fa19654a0248f7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb576da94c2948d3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7540,7 +7540,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R12c42006074c4cb7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbad17dfcbc394a2b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7819,7 +7819,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e34aa25f1bc48fe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R556858104f134a9d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8196,7 +8196,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R90ea52645e014e41"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R516788443e664a8c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8524,7 +8524,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra9f08a33b3394d47"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9988e34951a4808"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9048,7 +9048,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf35482209cba4db6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb83d117b00fe4b0b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9474,7 +9474,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6070efe3fa644e0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6121c0d81ded4517"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9908,7 +9908,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R385f9410d9724231"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57be8b6769fc4ec1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10648,7 +10648,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6665b05dccf54566"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b95756369a9454e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11388,7 +11388,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R144874bc233c48c6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79ca26449886414a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11822,7 +11822,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R478988a965e4477a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda739a573c7e46b9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12297,7 +12297,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb9da72c007154453"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfda0d4283b854d53"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12919,7 +12919,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42ab31b60e524121"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R219dfa6c9b4e4c36"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13729,7 +13729,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf86284fc681d4072"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c3397a750d34ead"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14294,7 +14294,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f19374a92424a34"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b7301dce26b4a78"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16032,7 +16032,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d879fcae207432e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1898ea48d94d43e8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16360,7 +16360,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00f821d96c4944a1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf554cb0d757d478a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16737,7 +16737,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd727b5359a3a4587"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9e770bbe3e34637"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17375,7 +17375,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra5f884221a8e4287"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re12c50b23e1148d2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18029,7 +18029,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re751602224694c84"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reaf65e6b27b0458e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18667,7 +18667,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R33ae8f65555d43ac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R24aa715c5dfb4a2c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18946,7 +18946,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R324eac1baa7346e6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R146f8b1ae5f848d6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Ascension_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Ascension_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Red9224dfd54b449c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R8d178b4739a648d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R23bf7050dcab4bc9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R892414026212457e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R672222205a60419c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R7847de510ae14f8b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R3671dc483f964e2d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Rab90b7272b1c4de3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R9c8b9aa01e0b4acc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="Rf0015377e6e3454b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Rfb56fe9869e94693"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R1fe181a7afec4c71"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R5ffe54f98b404ff6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R0d8d8490d8b2432e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R64ff6caea5554430"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R6bd0e8ac2a0a48a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="Rd3856b94ef86474a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R2221a7f776eb4595"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R848da0d2ab7a4c55"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Rc7c2e2f9f3a643e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R454eb6a8102449bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="Ra609b4e9b31f49d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R0560a8d589724a3d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R8348605e1ef0487e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="Reded0d6c834d4f26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Reb54ec9de5e045d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R30cf1999e3c64ca1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="Rca9970c2d63248b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rff1b8cf1d93a4e3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R75f17e3accc64c36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Rcfe9f465c0ff45f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Reb9bd7ca95db457f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Re1b25732c0724270"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="Rc1df1b4e24014c46"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R1f5afcc9f4eb4c89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Re1409074a8f34313"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Rc98da41c8d2c471f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R83b5ec28b1104862"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Rb859941572b144a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R915fc3ca8e8e4e05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R29953b167ed64149"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R2dccb34d92a84ec5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R16797d15319548c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R1770b60300484220"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R56d66f0f10714114"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R69fd75ff9cd04eaf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R46fb9763d0f14ec2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R042a85d377fc4872"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R58438abbe696424d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="Rc6ae91b4a5264f13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R8e6cc0a1cab74ddc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R8741ef88c4274167"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="Re6e4e5feebf1422e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R8951dea605a64ad6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Rcda5241d6e754770"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="Rce56d21c1c104c2c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4228,7 +4228,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1de341eee8594898"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7027ce16660c47a9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4866,7 +4866,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4bd8c29c13214cb1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6116af556e3e4845"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5504,7 +5504,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R90718b1a17f44258"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39eeee581d2a4351"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6142,7 +6142,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc7f3382ad58a438f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R188f6c549fe94e05"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6902,7 +6902,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb576da94c2948d3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raeeed415a74c44d1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7540,7 +7540,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbad17dfcbc394a2b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea583218d91a4242"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7819,7 +7819,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R556858104f134a9d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a1857009f344a8d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8196,7 +8196,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R516788443e664a8c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd15f4068d8344491"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8524,7 +8524,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9988e34951a4808"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55a8ffbc85f34444"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9048,7 +9048,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb83d117b00fe4b0b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07b5eec4f74d41f7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9474,7 +9474,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6121c0d81ded4517"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R10125d7a90164093"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9908,7 +9908,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57be8b6769fc4ec1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47c3a86d4d8a4f44"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10648,7 +10648,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b95756369a9454e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6efd1468167f4083"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11388,7 +11388,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79ca26449886414a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R48dea5f9d48a4e30"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11822,7 +11822,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda739a573c7e46b9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R426764c04e614a48"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12297,7 +12297,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfda0d4283b854d53"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95f0d67095f94684"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12919,7 +12919,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R219dfa6c9b4e4c36"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5102270ac4974f09"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13729,7 +13729,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c3397a750d34ead"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra13ccf4d35f4413d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14294,7 +14294,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b7301dce26b4a78"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a6a0dd34c934fa6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16032,7 +16032,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1898ea48d94d43e8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd806fe4035343a5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16360,7 +16360,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf554cb0d757d478a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f16eb20029842e1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16737,7 +16737,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9e770bbe3e34637"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re894a487dd134cf8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17375,7 +17375,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re12c50b23e1148d2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra2b1f3957d6245b9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18029,7 +18029,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reaf65e6b27b0458e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R156f6b3e69ab4658"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18667,7 +18667,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R24aa715c5dfb4a2c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea4c6728f23a486f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18946,7 +18946,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R146f8b1ae5f848d6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc8943f3ce8ed4ba2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Ascension_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Ascension_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rff1b8cf1d93a4e3a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R75f17e3accc64c36"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Rcfe9f465c0ff45f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Reb9bd7ca95db457f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Re1b25732c0724270"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="Rc1df1b4e24014c46"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R1f5afcc9f4eb4c89"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Re1409074a8f34313"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Rc98da41c8d2c471f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R83b5ec28b1104862"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Rb859941572b144a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R915fc3ca8e8e4e05"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R29953b167ed64149"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R2dccb34d92a84ec5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R16797d15319548c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R1770b60300484220"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R56d66f0f10714114"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R69fd75ff9cd04eaf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R46fb9763d0f14ec2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R042a85d377fc4872"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R58438abbe696424d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="Rc6ae91b4a5264f13"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R8e6cc0a1cab74ddc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R8741ef88c4274167"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="Re6e4e5feebf1422e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R8951dea605a64ad6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Rcda5241d6e754770"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="Rce56d21c1c104c2c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R4cf469d9b53c4f29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R90ec490f67124a4f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R64d7ae8fb4f74a43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Rd3d4ade5e7c44bbc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R626b018513c74078"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R863e6af6a8864dd6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R393ebd3c2522405f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Rd526f4104db44711"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R2a557d965b354d99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R2eaf3447d106410d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R52df17aa583748d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R6cbd52303e254756"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="Rfdeb05b1e062496e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="Rb7a544decce640e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R6284809731b64758"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="Rcb53ac84b9f54595"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="Rbc3386fbe6304847"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Rb6153a2e71554819"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="Ra7c9b1e68f6a4003"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R41229e7212da4ac0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Ra02abdcb8e4340a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R93dbe6c0a4624347"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R1c33dd56ffe04f27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R22209ec571764d3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R05f73bf2f46e40e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R1825f5b8d7334180"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Rfb20fd41af284fa6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R47fc97c8706e456a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4228,7 +4228,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7027ce16660c47a9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9cae399084474ca2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4866,7 +4866,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6116af556e3e4845"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb840995d3a584a6c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5504,7 +5504,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39eeee581d2a4351"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8e23b787aec84d77"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6142,7 +6142,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R188f6c549fe94e05"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b39a9beea9b4a9b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6902,7 +6902,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raeeed415a74c44d1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57ae1dc615c240c3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7540,7 +7540,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea583218d91a4242"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb596870f74af4723"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7819,7 +7819,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a1857009f344a8d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9604cf9ba984a06"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8196,7 +8196,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd15f4068d8344491"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6475e5c6458a46c2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8524,7 +8524,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55a8ffbc85f34444"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73b65d274f304acc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9048,7 +9048,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07b5eec4f74d41f7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b29ce49be9b433b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9474,7 +9474,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R10125d7a90164093"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe1e9fe949ef4864"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9908,7 +9908,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47c3a86d4d8a4f44"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88d1e937e28a4a72"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10648,7 +10648,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6efd1468167f4083"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R507d44ac6e744a10"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11388,7 +11388,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R48dea5f9d48a4e30"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8da48eb144fc4ea7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11822,7 +11822,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R426764c04e614a48"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra149ade1fe5547d3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12297,7 +12297,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95f0d67095f94684"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc09a0aac86d24413"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12919,7 +12919,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5102270ac4974f09"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree9af28682114172"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13729,7 +13729,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra13ccf4d35f4413d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77a65b278e664070"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14294,7 +14294,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a6a0dd34c934fa6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R565e0368a04f4234"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16032,7 +16032,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd806fe4035343a5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R060a2076e72548d3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16360,7 +16360,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f16eb20029842e1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54e4e3bb11494ed6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16737,7 +16737,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re894a487dd134cf8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c174aa52e56431e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17375,7 +17375,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra2b1f3957d6245b9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc263bb9e894b4f4b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18029,7 +18029,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R156f6b3e69ab4658"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac8d6e1d35694e3f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18667,7 +18667,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea4c6728f23a486f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf030b0e5efe74b53"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18946,7 +18946,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc8943f3ce8ed4ba2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e5b2c955c734a66"/>
   </x:tableParts>
 </x:worksheet>
 </file>